--- a/excel/hermite.xlsx
+++ b/excel/hermite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamilton\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6EAF03-972C-4194-8C7A-37BB9180F4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A946F3-62B3-4A2E-8046-E24D8FC7269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7815" yWindow="1350" windowWidth="18285" windowHeight="12375" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="2820" windowWidth="18285" windowHeight="12375" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rf_0.5_0-3_ndiv" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -527,7 +530,7 @@
         <v>-2.2065312144585993</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3">
         <v>-0.6020599913279624</v>
       </c>
@@ -538,9 +541,9 @@
         <v>-3.0481583515671464</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
       </c>
       <c r="B4">
         <v>-1.9820211514864106</v>
@@ -549,7 +552,7 @@
         <v>-3.8251512239752445</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5">
         <v>-1.2041199826559248</v>
       </c>
@@ -557,7 +560,7 @@
         <v>-2.4379912743252716</v>
       </c>
       <c r="C5">
-        <v>-4.583310279735629</v>
+        <v>-4.5833102797356293</v>
       </c>
     </row>
     <row r="8" spans="1:4" dyDescent="0.2">
@@ -574,10 +577,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8316BB8-363F-4E0A-A57F-BFF2D7C476E6}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:3" dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,41 +588,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="B2">
-        <v>-1.3305670619669649</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+        <v>-0.3847156903640109</v>
+      </c>
+      <c r="C2">
+        <v>-1.3305670366102806</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>-2.2065312144588227</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+        <v>-0.9640523240422519</v>
+      </c>
+      <c r="C3">
+        <v>-2.2065310862118985</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>-3.0481583515663124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+        <v>-1.5091375293653544</v>
+      </c>
+      <c r="C4">
+        <v>-3.04815815020485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.90308998699194354</v>
+        <v>-0.9030899869919435</v>
       </c>
       <c r="B5">
-        <v>-3.8251512239799439</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
-      <c r="D7" t="s">
-        <v>2</v>
+        <v>-1.9820211739583096</v>
+      </c>
+      <c r="C5">
+        <v>-3.8251508820779745</v>
       </c>
     </row>
   </sheetData>
@@ -639,7 +649,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>-1.2468093649752947</v>
+        <v>-0.11824774425144652</v>
+      </c>
+      <c r="C2">
+        <v>-1.0736431490211722</v>
       </c>
     </row>
     <row r="3" spans="1:4" dyDescent="0.2">
@@ -647,7 +660,10 @@
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>-1.8240714546936463</v>
+        <v>-0.18109783629418974</v>
+      </c>
+      <c r="C3">
+        <v>-1.3692609170638281</v>
       </c>
     </row>
     <row r="4" spans="1:4" dyDescent="0.2">
@@ -655,7 +671,10 @@
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>-1.8275181024379106</v>
+        <v>0.18328124001673207</v>
+      </c>
+      <c r="C4">
+        <v>-1.3644999446608517</v>
       </c>
     </row>
     <row r="5" spans="1:4" dyDescent="0.2">
@@ -663,7 +682,10 @@
         <v>-0.90308998699194354</v>
       </c>
       <c r="B5">
-        <v>-1.9101471428866734</v>
+        <v>-0.56028743895306821</v>
+      </c>
+      <c r="C5">
+        <v>-2.317898382468333</v>
       </c>
     </row>
     <row r="7" spans="1:4" dyDescent="0.2">
